--- a/data/conf_ta_output/conf_ta_c.xlsx
+++ b/data/conf_ta_output/conf_ta_c.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -416,7 +416,7 @@
         <v>100</v>
       </c>
       <c r="B2">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C2">
         <v>0.01</v>
@@ -425,10 +425,10 @@
         <v>1000</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>0.05</v>
@@ -440,7 +440,7 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>0.063</v>
+        <v>0.095</v>
       </c>
       <c r="K2">
         <v>1000</v>
@@ -451,19 +451,19 @@
         <v>100</v>
       </c>
       <c r="B3">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C3">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="D3">
         <v>1000</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G3">
         <v>0.05</v>
@@ -475,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>0.07000000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K3">
         <v>1000</v>
@@ -486,19 +486,19 @@
         <v>100</v>
       </c>
       <c r="B4">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D4">
         <v>1000</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>0.05</v>
@@ -510,7 +510,7 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>0.073</v>
+        <v>0.099</v>
       </c>
       <c r="K4">
         <v>1000</v>
@@ -521,19 +521,19 @@
         <v>100</v>
       </c>
       <c r="B5">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C5">
-        <v>0.075</v>
+        <v>0.15</v>
       </c>
       <c r="D5">
         <v>1000</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>0.05</v>
@@ -545,7 +545,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>0.07199999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="K5">
         <v>1000</v>
@@ -556,19 +556,19 @@
         <v>100</v>
       </c>
       <c r="B6">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C6">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D6">
         <v>1000</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>0.05</v>
@@ -580,7 +580,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>0.06900000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="K6">
         <v>1000</v>
@@ -591,19 +591,19 @@
         <v>100</v>
       </c>
       <c r="B7">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C7">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="D7">
         <v>1000</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>0.05</v>
@@ -615,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>0.077</v>
+        <v>0.096</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -626,19 +626,19 @@
         <v>100</v>
       </c>
       <c r="B8">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C8">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="D8">
         <v>1000</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>0.05</v>
@@ -650,7 +650,7 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>0.073</v>
+        <v>0.094</v>
       </c>
       <c r="K8">
         <v>1000</v>
@@ -661,19 +661,19 @@
         <v>100</v>
       </c>
       <c r="B9">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C9">
-        <v>0.175</v>
+        <v>0.35</v>
       </c>
       <c r="D9">
         <v>1000</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>0.05</v>
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>0.077</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K9">
         <v>1000</v>
@@ -696,19 +696,19 @@
         <v>100</v>
       </c>
       <c r="B10">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
         <v>1000</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>0.05</v>
@@ -720,149 +720,9 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>0.07099999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="K10">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>100</v>
-      </c>
-      <c r="B11">
-        <v>0.02</v>
-      </c>
-      <c r="C11">
-        <v>0.225</v>
-      </c>
-      <c r="D11">
-        <v>1000</v>
-      </c>
-      <c r="E11">
-        <v>100</v>
-      </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>0.05</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>0.059</v>
-      </c>
-      <c r="K11">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>100</v>
-      </c>
-      <c r="B12">
-        <v>0.02</v>
-      </c>
-      <c r="C12">
-        <v>0.25</v>
-      </c>
-      <c r="D12">
-        <v>1000</v>
-      </c>
-      <c r="E12">
-        <v>100</v>
-      </c>
-      <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>0.05</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>0.076</v>
-      </c>
-      <c r="K12">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>100</v>
-      </c>
-      <c r="B13">
-        <v>0.02</v>
-      </c>
-      <c r="C13">
-        <v>0.275</v>
-      </c>
-      <c r="D13">
-        <v>1000</v>
-      </c>
-      <c r="E13">
-        <v>100</v>
-      </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>0.05</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>0.053</v>
-      </c>
-      <c r="K13">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>100</v>
-      </c>
-      <c r="B14">
-        <v>0.02</v>
-      </c>
-      <c r="C14">
-        <v>0.3</v>
-      </c>
-      <c r="D14">
-        <v>1000</v>
-      </c>
-      <c r="E14">
-        <v>100</v>
-      </c>
-      <c r="F14">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>0.05</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>0.054</v>
-      </c>
-      <c r="K14">
         <v>1000</v>
       </c>
     </row>
